--- a/login_credentials.xlsx
+++ b/login_credentials.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00163A70"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,44 +413,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Jurisdiction</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Username</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Password</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Full Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Designation</t>
         </is>
@@ -476,22 +464,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Anantapur</t>
+          <t>Alluri Sitharama Raju</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>anantapur</t>
+          <t>alluri_sitharama_raju</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Antp@2025</t>
+          <t>ASRj@2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anantapur DRSC Unit</t>
+          <t>Alluri Sitharama Raju DRSC Unit</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -508,22 +496,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chittoor</t>
+          <t>Anakapalli</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>chittoor</t>
+          <t>anakapalli</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Chtr@2025</t>
+          <t>Ankp@2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chittoor DRSC Unit</t>
+          <t>Anakapalli DRSC Unit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -540,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>East Godavari</t>
+          <t>Ananthapuram</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>east_godavari</t>
+          <t>ananthapuram</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EGod@2025</t>
+          <t>Antm@2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Godavari DRSC Unit</t>
+          <t>Ananthapuram DRSC Unit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,22 +560,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Guntur</t>
+          <t>Ananthapuramu EXCISE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>guntur</t>
+          <t>ananthapuramu_excise</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gntr@2025</t>
+          <t>AExc@2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Guntur DRSC Unit</t>
+          <t>Ananthapuramu EXCISE DRSC Unit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -604,22 +592,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Annamayya</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>krishna</t>
+          <t>annamayya</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Krsh@2025</t>
+          <t>Anny@2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Krishna DRSC Unit</t>
+          <t>Annamayya DRSC Unit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,22 +624,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kurnool</t>
+          <t>Annamayya EXCISE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kurnool</t>
+          <t>annamayya_excise</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Krnl@2025</t>
+          <t>NExc@2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kurnool DRSC Unit</t>
+          <t>Annamayya EXCISE DRSC Unit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -668,22 +656,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nellore</t>
+          <t>Bapatla</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nellore</t>
+          <t>bapatla</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nllr@2025</t>
+          <t>Bptl@2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nellore DRSC Unit</t>
+          <t>Bapatla DRSC Unit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -700,22 +688,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prakasam</t>
+          <t>Bapatla EXCISE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>prakasam</t>
+          <t>bapatla_excise</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Prkm@2025</t>
+          <t>BExc@2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prakasam DRSC Unit</t>
+          <t>Bapatla EXCISE DRSC Unit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -732,22 +720,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Srikakulam</t>
+          <t>C I D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>srikakulam</t>
+          <t>c_i_d</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sklm@2025</t>
+          <t>CID@2025x</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Srikakulam DRSC Unit</t>
+          <t>C I D DRSC Unit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,22 +752,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visakhapatnam</t>
+          <t>Chittoor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>visakhapatnam</t>
+          <t>chittoor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vskp@2025</t>
+          <t>Chtr@2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Visakhapatnam DRSC Unit</t>
+          <t>Chittoor DRSC Unit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -796,22 +784,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vizianagaram</t>
+          <t>Chittoor  EXCISE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>vizianagaram</t>
+          <t>chittoor_excise</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Vzng@2025</t>
+          <t>CExc@2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vizianagaram DRSC Unit</t>
+          <t>Chittoor EXCISE DRSC Unit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -828,22 +816,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>West Godavari</t>
+          <t>Coastal Security Police</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>west_godavari</t>
+          <t>coastal_security_police</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WGod@2025</t>
+          <t>CSP@2025x</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Godavari DRSC Unit</t>
+          <t>Coastal Security Police DRSC Unit</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -860,22 +848,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YSR Kadapa</t>
+          <t>Dr. B R Ambedkar Konaseema</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ysr_kadapa</t>
+          <t>dr_b_r_ambedkar_konaseema</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kdpa@2025</t>
+          <t>DBRK@2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>YSR Kadapa DRSC Unit</t>
+          <t>Dr. B R Ambedkar Konaseema DRSC Unit</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -892,22 +880,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bapatla</t>
+          <t>Dr. B R Ambedkar Konaseema EXCISE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bapatla</t>
+          <t>dr_b_r_ambedkar_konaseema_excise</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bptl@2025</t>
+          <t>DKEx@2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bapatla DRSC Unit</t>
+          <t>Dr. B R Ambedkar Konaseema EXCISE DRSC Unit</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -924,22 +912,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eluru</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>eluru</t>
+          <t>eagle</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Elru@2025</t>
+          <t>Eagl@2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eluru DRSC Unit</t>
+          <t>Eagle DRSC Unit</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -956,22 +944,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kakinada</t>
+          <t>East Godavari</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kakinada</t>
+          <t>east_godavari</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kknd@2025</t>
+          <t>EGod@2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kakinada DRSC Unit</t>
+          <t>East Godavari DRSC Unit</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -988,22 +976,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Konaseema</t>
+          <t>East Godavari EXCISE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>konaseema</t>
+          <t>east_godavari_excise</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Knsm@2025</t>
+          <t>EGEx@2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Konaseema DRSC Unit</t>
+          <t>East Godavari EXCISE DRSC Unit</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1020,22 +1008,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nandyal</t>
+          <t>Eluru</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nandyal</t>
+          <t>eluru</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ndyl@2025</t>
+          <t>Elru@2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nandyal DRSC Unit</t>
+          <t>Eluru DRSC Unit</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1052,22 +1040,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>GRP Guntakal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ntr</t>
+          <t>grp_guntakal</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ntr@2025x</t>
+          <t>GRPG@2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NTR DRSC Unit</t>
+          <t>GRP Guntakal DRSC Unit</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1084,22 +1072,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Palnadu</t>
+          <t>GRP Vijayawada</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>palnadu</t>
+          <t>grp_vijayawada</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Plnd@2025</t>
+          <t>GRPV@2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palnadu DRSC Unit</t>
+          <t>GRP Vijayawada DRSC Unit</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1116,22 +1104,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Parvathipuram Manyam</t>
+          <t>Guntur</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>parvathipuram_manyam</t>
+          <t>guntur</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PvMy@2025</t>
+          <t>Gntr@2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Parvathipuram Manyam DRSC Unit</t>
+          <t>Guntur DRSC Unit</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1148,22 +1136,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sri Sathya Sai</t>
+          <t>Intelligence  Unit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sri_sathya_sai</t>
+          <t>intelligence_unit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SSSi@2025</t>
+          <t>INTU@2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sri Sathya Sai DRSC Unit</t>
+          <t>Intelligence Unit DRSC Unit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1180,22 +1168,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tirupati</t>
+          <t>Kakinada</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>tirupati</t>
+          <t>kakinada</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Trpt@2025</t>
+          <t>Kknd@2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tirupati DRSC Unit</t>
+          <t>Kakinada DRSC Unit</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1212,22 +1200,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Anakapalli</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>anakapalli</t>
+          <t>krishna</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ankp@2025</t>
+          <t>Krsh@2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Anakapalli DRSC Unit</t>
+          <t>Krishna DRSC Unit</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1244,22 +1232,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alluri Sitharama Raju</t>
+          <t>Kurnool</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>alluri_sitharama_raju</t>
+          <t>kurnool</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ASRj@2025</t>
+          <t>Krnl@2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alluri Sitharama Raju DRSC Unit</t>
+          <t>Kurnool DRSC Unit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1271,62 +1259,606 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DGP</t>
+          <t>District</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>State HQ</t>
+          <t>Markapuram</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dgp</t>
+          <t>markapuram</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DGP@admin2025</t>
+          <t>Mrkp@2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Director General of Police</t>
+          <t>Markapuram DRSC Unit</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DGP</t>
+          <t>District DRSC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NTR Commissionerate</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ntr_commissionerate</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NTRC@2025</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NTR Commissionerate DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nandyal</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>nandyal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ndyl@2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Nandyal DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Palnadu</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>palnadu</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plnd@2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Palnadu DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Parvathipuram Manyam</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>parvathipuram_manyam</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PvMy@2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Parvathipuram Manyam DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Polavaram</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>polavaram</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plvr@2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Polavaram DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Prakasam</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>prakasam</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Prkm@2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Prakasam DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Red Sanders Anti-Smuggling Task Force</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>red_sanders_anti_smuggling_task_force</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RSAT@2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Red Sanders Anti-Smuggling Task Force DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sri Potti Sriramulu Nellore</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>sri_potti_sriramulu_nellore</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SPSN@2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sri Potti Sriramulu Nellore DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sri Sathya Sai</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sri_sathya_sai</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SSSi@2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sri Sathya Sai DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Srikakulam</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>srikakulam</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sklm@2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Srikakulam DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tirupathi</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>tirupathi</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Trpt@2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Tirupathi DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Visakhapatnam Commissionerate</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>visakhapatnam_commissionerate</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VSPC@2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Visakhapatnam Commissionerate DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Vizianagaram</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>vizianagaram</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Vzng@2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Vizianagaram DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>West Godavari</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>west_godavari</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>WGod@2025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>West Godavari DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>YSR Kadapa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ysr_kadapa</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Kdpa@2025</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>YSR Kadapa DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Prism</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>prism</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Prsm@2025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Prism DRSC Unit</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>District DRSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DGP</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>State HQ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dgp</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DGP@admin2025</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Director General of Police</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>ADGP</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>State HQ</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>adgp</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>ADGP@admin2025</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Additional DGP</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>ADGP</t>
         </is>
